--- a/courses/BUS-314-International-Corporate-Finance/accounting-ratios/_scenarios/BUS314_CAT_Scenario.xlsx
+++ b/courses/BUS-314-International-Corporate-Finance/accounting-ratios/_scenarios/BUS314_CAT_Scenario.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\shidler\BUS-314-International-Corporate-Finance\accounting-ratios\_scenarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\shidler\courses\BUS-314-International-Corporate-Finance\accounting-ratios\_scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD959C9-7A82-44A9-A2BB-EF5B9BB2E24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031443C3-FA8E-42D4-A778-75C91182DCB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,7 +80,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -89,7 +89,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2024, SEC EDGAR earnings release, https://www.sec.gov/Archives/edgar/data/18230/000001823025000004/cat_exx991x4qx2024xearning.htm</t>
@@ -104,7 +104,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -113,10 +113,58 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2023, SEC EDGAR, https://www.sec.gov/Archives/edgar/data/18230/000001823025000004/cat_exx991x4qx2024xearning.htm</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{FE27CEE7-40D0-4CC7-906F-1539F8CD9D4E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2024, SEC EDGAR, https://www.sec.gov/Archives/edgar/data/18230/000001823025000008/cat-20241231.htm</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{BD3D2B3A-8BED-4CE7-B279-64C9BCC8FA43}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2023, SEC EDGAR</t>
         </r>
       </text>
     </comment>
@@ -128,7 +176,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -137,7 +185,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2024, SEC EDGAR earnings release, https://www.sec.gov/Archives/edgar/data/18230/000001823025000004/cat_exx991x4qx2024xearning.htm</t>
@@ -152,7 +200,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -161,10 +209,58 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2023, SEC EDGAR, https://www.sec.gov/Archives/edgar/data/18230/000001823025000004/cat_exx991x4qx2024xearning.htm</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G6" authorId="0" shapeId="0" xr:uid="{AD1B32B3-5E78-4C49-89FB-D5ADC156AE66}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2024, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H6" authorId="0" shapeId="0" xr:uid="{022F5D0B-3BBB-4897-99DF-2AE0A72D8FE1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2023, SEC EDGAR</t>
         </r>
       </text>
     </comment>
@@ -176,7 +272,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -185,7 +281,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2024, SEC EDGAR earnings release, https://www.sec.gov/Archives/edgar/data/18230/000001823025000004/cat_exx991x4qx2024xearning.htm</t>
@@ -200,7 +296,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -209,10 +305,58 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2023, SEC EDGAR, https://www.sec.gov/Archives/edgar/data/18230/000001823025000004/cat_exx991x4qx2024xearning.htm</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{B9BC9C48-F1C7-4666-992D-E554ECD602B5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2024, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H7" authorId="0" shapeId="0" xr:uid="{761089E3-28A6-416B-B053-5B5786B0BF75}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2023, SEC EDGAR</t>
         </r>
       </text>
     </comment>
@@ -224,7 +368,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -233,7 +377,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2024, SEC EDGAR earnings release, https://www.sec.gov/Archives/edgar/data/18230/000001823025000004/cat_exx991x4qx2024xearning.htm</t>
@@ -248,7 +392,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -257,10 +401,58 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2023, SEC EDGAR, https://www.sec.gov/Archives/edgar/data/18230/000001823025000004/cat_exx991x4qx2024xearning.htm</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{6996A405-CE86-425C-BEDB-73FF0A9B63B7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2024, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{A6655071-10DB-4AC6-B1D4-3250BF8EF4B2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2023, SEC EDGAR</t>
         </r>
       </text>
     </comment>
@@ -272,7 +464,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -281,7 +473,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2024, prepaid expenses and other current assets, SEC EDGAR, https://www.sec.gov/Archives/edgar/data/18230/000001823025000004/cat_exx991x4qx2024xearning.htm</t>
@@ -296,7 +488,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -305,10 +497,154 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2023, prepaid expenses and other current assets, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G9" authorId="0" shapeId="0" xr:uid="{E3A0214C-B5E3-465B-8649-CBA4A7C10720}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2024, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{F2B57A7F-6873-47AD-A71F-C5432212DA8E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2023, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{6DE17B6C-3BBF-4B4D-AB3B-0DE500BBB241}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2024, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H10" authorId="0" shapeId="0" xr:uid="{7E23809B-DF22-4AD8-A50D-867B0DA36694}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2023, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{B4D7E2BD-6A27-4687-8CBA-05950E3709CF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2024, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{0D7B9292-6068-4C46-8A31-1C1DE8F9AA5A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2023, SEC EDGAR</t>
         </r>
       </text>
     </comment>
@@ -320,7 +656,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -329,7 +665,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2024 (gross PP&amp;E), SEC EDGAR 10-K filing, https://www.sec.gov/Archives/edgar/data/18230/000001823025000008/cat-20241231.htm</t>
@@ -344,7 +680,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -353,10 +689,58 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2023 (gross PP&amp;E), SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G12" authorId="0" shapeId="0" xr:uid="{24CAE528-254E-4E42-959D-E1A5C3F37135}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2024, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H12" authorId="0" shapeId="0" xr:uid="{525C74F2-BF24-4269-B0B9-DEA87E658FC8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2023, SEC EDGAR</t>
         </r>
       </text>
     </comment>
@@ -368,7 +752,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -377,7 +761,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2024 (accumulated depreciation), SEC EDGAR 10-K filing</t>
@@ -392,7 +776,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -401,10 +785,58 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2023 (accumulated depreciation), SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G15" authorId="0" shapeId="0" xr:uid="{CAE32DF5-2380-42A6-9EA8-F9781A70B2FA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2024, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H15" authorId="0" shapeId="0" xr:uid="{91FF2D9E-FD8A-4456-A01C-D53E88DEDEFA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2023, SEC EDGAR</t>
         </r>
       </text>
     </comment>
@@ -416,7 +848,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -425,7 +857,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2024: LT trade recv $1,225M + LT finance recv $13,242M, SEC EDGAR, https://www.sec.gov/Archives/edgar/data/18230/000001823025000004/cat_exx991x4qx2024xearning.htm</t>
@@ -440,7 +872,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -449,10 +881,58 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2023: LT trade recv $1,238M + LT finance recv $12,664M, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{A000D51A-5B3B-4638-BBD6-571C1F01A45D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2024, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H16" authorId="0" shapeId="0" xr:uid="{C177CB72-3215-4C78-8B75-62CDFAF06B8A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2023, SEC EDGAR</t>
         </r>
       </text>
     </comment>
@@ -464,7 +944,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -473,7 +953,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2024, SEC EDGAR, https://www.sec.gov/Archives/edgar/data/18230/000001823025000004/cat_exx991x4qx2024xearning.htm</t>
@@ -488,7 +968,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -497,14 +977,14 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2023, SEC EDGAR</t>
         </r>
       </text>
     </comment>
-    <comment ref="C21" authorId="0" shapeId="0" xr:uid="{DAE48935-4CCF-4E5A-8273-2D24C44B6064}">
+    <comment ref="G17" authorId="0" shapeId="0" xr:uid="{730CB927-C201-4613-A11C-FE6A9A65AA01}">
       <text>
         <r>
           <rPr>
@@ -522,13 +1002,61 @@
             <color indexed="81"/>
             <rFont val="Tahoma"/>
             <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2024, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H17" authorId="0" shapeId="0" xr:uid="{25532C04-2CC1-45F3-B63A-7CABBE089CC0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2023, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C20" authorId="0" shapeId="0" xr:uid="{DAE48935-4CCF-4E5A-8273-2D24C44B6064}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2024: Goodwill $5,241M + Intangibles $399M, SEC EDGAR earnings release, https://www.sec.gov/Archives/edgar/data/18230/000001823025000004/cat_exx991x4qx2024xearning.htm</t>
         </r>
       </text>
     </comment>
-    <comment ref="D21" authorId="0" shapeId="0" xr:uid="{5A4AE0EB-4691-408F-BF71-40BCD41E2455}">
+    <comment ref="D20" authorId="0" shapeId="0" xr:uid="{5A4AE0EB-4691-408F-BF71-40BCD41E2455}">
       <text>
         <r>
           <rPr>
@@ -536,7 +1064,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -545,14 +1073,14 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2023: Goodwill $5,308M + Intangibles $564M, SEC EDGAR</t>
         </r>
       </text>
     </comment>
-    <comment ref="C22" authorId="0" shapeId="0" xr:uid="{A183F507-2AD8-4762-8294-E1D5EC8707A3}">
+    <comment ref="C21" authorId="0" shapeId="0" xr:uid="{A183F507-2AD8-4762-8294-E1D5EC8707A3}">
       <text>
         <r>
           <rPr>
@@ -560,7 +1088,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -569,14 +1097,14 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2024, other assets (non-current), SEC EDGAR, https://www.sec.gov/Archives/edgar/data/18230/000001823025000004/cat_exx991x4qx2024xearning.htm</t>
         </r>
       </text>
     </comment>
-    <comment ref="D22" authorId="0" shapeId="0" xr:uid="{5CC338D1-2A3E-443D-ADE8-94F322EDC53E}">
+    <comment ref="D21" authorId="0" shapeId="0" xr:uid="{5CC338D1-2A3E-443D-ADE8-94F322EDC53E}">
       <text>
         <r>
           <rPr>
@@ -584,7 +1112,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -593,10 +1121,284 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Caterpillar 10-K FY2023, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G21" authorId="0" shapeId="0" xr:uid="{A8FC0104-4BDB-4443-9869-D660C2CE2524}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2024, SEC EDGAR, https://www.sec.gov/Archives/edgar/data/18230/000001823025000008/cat-20241231.htm</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H21" authorId="0" shapeId="0" xr:uid="{CDA84699-4239-40B6-AE29-A7A1D9F8A8C9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2023, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G22" authorId="0" shapeId="0" xr:uid="{1E3B0E51-9824-4202-8D81-FE1EBBF98FBA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2024, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H22" authorId="0" shapeId="0" xr:uid="{A1EF85E8-C528-4DFF-8CB1-841BA1050CA1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2023, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G23" authorId="0" shapeId="0" xr:uid="{FB5C20FF-9356-4D3C-97B2-2DF0FF9BFDF5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2024 (Profit employed in the business), SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H23" authorId="0" shapeId="0" xr:uid="{7E711107-F6C5-4D59-9306-B8B675B627AF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2023 (Profit employed in the business), SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G24" authorId="0" shapeId="0" xr:uid="{24708545-A849-4240-A273-7DAFF16442F4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2024, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H24" authorId="0" shapeId="0" xr:uid="{C5F52DC2-B78B-48CD-B2FE-23053AA5DAF2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2023, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G25" authorId="0" shapeId="0" xr:uid="{1540885A-7844-4211-B1E0-F24C623E225E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2024, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H25" authorId="0" shapeId="0" xr:uid="{5493D405-3BB3-4FBD-8E02-6E23F90CB309}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2023, SEC EDGAR</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Adam Stauffer</author>
+  </authors>
+  <commentList>
+    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{D7A27CB3-46D1-4AFD-9C2B-563C447CD1F4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Adam Stauffer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Caterpillar 10-K FY2024 — SGA expenses, SEC EDGAR, https://www.sec.gov/Archives/edgar/data/18230/000001823025000008/cat-20241231.htm</t>
         </r>
       </text>
     </comment>
@@ -605,7 +1407,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="288">
   <si>
     <t>Balance Sheet — Caterpillar Inc. (CAT)</t>
   </si>
@@ -631,9 +1433,6 @@
     <t>Current Liabilities</t>
   </si>
   <si>
-    <t xml:space="preserve">   Debt due for repayment</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Accounts payable</t>
   </si>
   <si>
@@ -652,12 +1451,6 @@
     <t xml:space="preserve">   Total current assets</t>
   </si>
   <si>
-    <t xml:space="preserve">   Long-term debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Other long-term liabilities</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Property, plant, and equipment</t>
   </si>
   <si>
@@ -676,15 +1469,9 @@
     <t>Other Assets</t>
   </si>
   <si>
-    <t xml:space="preserve">   Common stock and paid-in capital</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Intangible assets (goodwill)</t>
   </si>
   <si>
-    <t xml:space="preserve">   Retained earnings</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Other assets</t>
   </si>
   <si>
@@ -1442,6 +2229,48 @@
   </si>
   <si>
     <t xml:space="preserve">   Deferred income taxes (noncurrent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Short-term borrowings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Accrued expenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Accrued wages, salaries &amp; benefits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Customer advances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Dividends payable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Long-term debt due within one year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Long-term debt due after one year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Liability for postemployment benefits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Other liabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Common stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Treasury stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Profit employed in the business</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Accumulated other comprehensive income (loss)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Noncontrolling interests</t>
   </si>
 </sst>
 </file>
@@ -1454,7 +2283,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1586,6 +2415,19 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1596,7 +2438,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1677,8 +2519,44 @@
         <fgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F5496"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E4F7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1701,11 +2579,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1731,9 +2646,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="18" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1816,8 +2728,42 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="18" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="18" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="7" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="19" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="20" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="18" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1902,10 +2848,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2099,7 +3041,9 @@
   <we:alternateReferences>
     <we:reference id="wa200009404" version="1.0.0.8" store="" storeType="OMEX"/>
   </we:alternateReferences>
-  <we:properties/>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;5fe9f014-5643-4129-bfee-c84d167e5ba8&quot;"/>
+  </we:properties>
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </we:webextension>
@@ -2107,7 +3051,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -2118,7 +3062,7 @@
     <col min="7" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" ht="19.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -2130,7 +3074,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A2" s="1"/>
       <c r="B2" s="3" t="s">
         <v>1</v>
@@ -2152,7 +3096,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A3" s="1"/>
       <c r="B3" s="6" t="s">
         <v>5</v>
@@ -2166,7 +3110,7 @@
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A4" s="1"/>
       <c r="B4" s="7" t="s">
         <v>6</v>
@@ -2174,16 +3118,16 @@
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-    </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+    </row>
+    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A5" s="1"/>
       <c r="B5" s="9" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C5" s="10">
         <v>6889</v>
@@ -2192,20 +3136,20 @@
         <v>6978</v>
       </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="10">
-        <v>9263</v>
-      </c>
-      <c r="H5" s="10">
-        <v>8574</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F5" s="46" t="s">
+        <v>274</v>
+      </c>
+      <c r="G5" s="50">
+        <v>4393</v>
+      </c>
+      <c r="H5" s="51">
+        <v>4643</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A6" s="1"/>
       <c r="B6" s="9" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C6" s="10">
         <v>9282</v>
@@ -2214,20 +3158,20 @@
         <v>9310</v>
       </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="10">
-        <v>3748</v>
-      </c>
-      <c r="H6" s="10">
-        <v>3892</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F6" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="50">
+        <v>7675</v>
+      </c>
+      <c r="H6" s="51">
+        <v>7906</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A7" s="1"/>
       <c r="B7" s="9" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C7" s="10">
         <v>9565</v>
@@ -2236,14 +3180,20 @@
         <v>9510</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-    </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F7" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="G7" s="50">
+        <v>5243</v>
+      </c>
+      <c r="H7" s="51">
+        <v>4958</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A8" s="1"/>
       <c r="B8" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="10">
         <v>16827</v>
@@ -2252,20 +3202,20 @@
         <v>16565</v>
       </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="10">
-        <v>7064</v>
-      </c>
-      <c r="H8" s="10">
-        <v>7213</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F8" s="46" t="s">
+        <v>276</v>
+      </c>
+      <c r="G8" s="50">
+        <v>2391</v>
+      </c>
+      <c r="H8" s="51">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="10">
         <v>3119</v>
@@ -2274,56 +3224,60 @@
         <v>4586</v>
       </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="12">
-        <f>SUM(G5:G8)</f>
-        <v>20075</v>
-      </c>
-      <c r="H9" s="12">
-        <f>SUM(H5:H8)</f>
-        <v>19679</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F9" s="46" t="s">
+        <v>277</v>
+      </c>
+      <c r="G9" s="50">
+        <v>2322</v>
+      </c>
+      <c r="H9" s="51">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A10" s="1"/>
       <c r="B10" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="13">
+        <v>13</v>
+      </c>
+      <c r="C10" s="12">
         <f>SUM(C5:C9)</f>
         <v>45682</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="12">
         <f>SUM(D5:D9)</f>
         <v>46949</v>
       </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F10" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="G10" s="50">
+        <v>674</v>
+      </c>
+      <c r="H10" s="51">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="5"/>
-      <c r="F11" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="10">
-        <v>25046</v>
-      </c>
-      <c r="H11" s="10">
-        <v>25107</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F11" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="50">
+        <v>2909</v>
+      </c>
+      <c r="H11" s="51">
+        <v>3123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A12" s="1"/>
       <c r="B12" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C12" s="8">
         <v>22574</v>
@@ -2332,20 +3286,20 @@
         <v>21497</v>
       </c>
       <c r="E12" s="5"/>
-      <c r="F12" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="10">
-        <v>8726</v>
-      </c>
-      <c r="H12" s="10">
-        <v>8684</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F12" s="46" t="s">
+        <v>279</v>
+      </c>
+      <c r="G12" s="50">
+        <v>6665</v>
+      </c>
+      <c r="H12" s="51">
+        <v>8763</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C13" s="10">
         <v>9213</v>
@@ -2354,14 +3308,22 @@
         <v>8817</v>
       </c>
       <c r="E13" s="5"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-    </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F13" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="52">
+        <f>SUM(G5:G12)</f>
+        <v>32272</v>
+      </c>
+      <c r="H13" s="53">
+        <f>SUM(H5:H12)</f>
+        <v>34728</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A14" s="1"/>
       <c r="B14" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C14" s="10">
         <f>C12-C13</f>
@@ -2372,234 +3334,270 @@
         <v>12680</v>
       </c>
       <c r="E14" s="5"/>
-      <c r="F14" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" s="12">
-        <f>G9+G11+G12</f>
-        <v>53847</v>
-      </c>
-      <c r="H14" s="12">
-        <f>H9+H11+H12</f>
-        <v>53470</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A15" s="1"/>
-      <c r="B15" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="13">
-        <f>C13-C14</f>
-        <v>-4148</v>
-      </c>
-      <c r="D15" s="13">
-        <f>D13-D14</f>
-        <v>-3863</v>
-      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F15" s="46" t="s">
+        <v>280</v>
+      </c>
+      <c r="G15" s="50">
+        <v>27351</v>
+      </c>
+      <c r="H15" s="51">
+        <v>24472</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A16" s="1"/>
       <c r="B16" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="C16" s="44">
+        <v>272</v>
+      </c>
+      <c r="C16" s="43">
         <v>14467</v>
       </c>
-      <c r="D16" s="44">
+      <c r="D16" s="43">
         <v>13902</v>
       </c>
       <c r="E16" s="5"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F16" s="46" t="s">
+        <v>281</v>
+      </c>
+      <c r="G16" s="50">
+        <v>3757</v>
+      </c>
+      <c r="H16" s="51">
+        <v>4098</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A17" s="1"/>
       <c r="B17" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="C17" s="44">
+        <v>273</v>
+      </c>
+      <c r="C17" s="43">
         <v>3312</v>
       </c>
-      <c r="D17" s="44">
+      <c r="D17" s="43">
         <v>2816</v>
       </c>
       <c r="E17" s="5"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F17" s="46" t="s">
+        <v>282</v>
+      </c>
+      <c r="G17" s="50">
+        <v>4890</v>
+      </c>
+      <c r="H17" s="51">
+        <v>4675</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="5"/>
-      <c r="F18" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F18" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="52">
+        <f>G13+G15+G16+G17</f>
+        <v>68270</v>
+      </c>
+      <c r="H18" s="53">
+        <f>H13+H15+H16+H17</f>
+        <v>67973</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A19" s="1"/>
       <c r="B19" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="5"/>
-      <c r="F19" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="10">
-        <v>2118</v>
-      </c>
-      <c r="H19" s="10">
-        <v>2118</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A20" s="1"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
+      <c r="B20" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="10">
+        <v>5640</v>
+      </c>
+      <c r="D20" s="10">
+        <v>5872</v>
+      </c>
       <c r="E20" s="5"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F20" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
+    </row>
+    <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A21" s="1"/>
-      <c r="B21" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="8">
-        <v>5640</v>
-      </c>
-      <c r="D21" s="8">
-        <v>5872</v>
+      <c r="B21" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="10">
+        <v>5302</v>
+      </c>
+      <c r="D21" s="10">
+        <v>5257</v>
       </c>
       <c r="E21" s="5"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-    </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F21" s="46" t="s">
+        <v>283</v>
+      </c>
+      <c r="G21" s="50">
+        <v>6941</v>
+      </c>
+      <c r="H21" s="51">
+        <v>6403</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A22" s="1"/>
       <c r="B22" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="10">
-        <v>5302</v>
-      </c>
-      <c r="D22" s="10">
-        <v>5257</v>
+        <v>21</v>
+      </c>
+      <c r="C22" s="13">
+        <f>SUM(C20:C21)</f>
+        <v>10942</v>
+      </c>
+      <c r="D22" s="13">
+        <f>SUM(D20:D21)</f>
+        <v>11129</v>
       </c>
       <c r="E22" s="5"/>
-      <c r="F22" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G22" s="10">
-        <v>30063</v>
-      </c>
-      <c r="H22" s="10">
-        <v>26844</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F22" s="46" t="s">
+        <v>284</v>
+      </c>
+      <c r="G22" s="50">
+        <v>-44331</v>
+      </c>
+      <c r="H22" s="51">
+        <v>-36339</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A23" s="1"/>
-      <c r="B23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="14">
-        <f>G25-C10-C15-C22</f>
-        <v>39192</v>
-      </c>
-      <c r="D23" s="14">
-        <f>H25-D10-D15-D22</f>
-        <v>34089</v>
-      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
       <c r="E23" s="5"/>
-      <c r="F23" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="G23" s="12">
-        <f>G19+G22</f>
-        <v>32181</v>
-      </c>
-      <c r="H23" s="12">
-        <f>H19+H22</f>
-        <v>28962</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F23" s="46" t="s">
+        <v>285</v>
+      </c>
+      <c r="G23" s="50">
+        <v>59352</v>
+      </c>
+      <c r="H23" s="51">
+        <v>51250</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
       <c r="E24" s="5"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-    </row>
-    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F24" s="46" t="s">
+        <v>286</v>
+      </c>
+      <c r="G24" s="50">
+        <v>-2471</v>
+      </c>
+      <c r="H24" s="51">
+        <v>-1820</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A25" s="1"/>
-      <c r="B25" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="16">
-        <f>C10+C15+C22+C23</f>
-        <v>86028</v>
-      </c>
-      <c r="D25" s="16">
-        <f>D10+D15+D22+D23</f>
-        <v>82432</v>
-      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
       <c r="E25" s="5"/>
-      <c r="F25" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="G25" s="16">
-        <f>G14+G23</f>
-        <v>86028</v>
-      </c>
-      <c r="H25" s="16">
-        <f>H14+H23</f>
-        <v>82432</v>
+      <c r="F25" s="46" t="s">
+        <v>287</v>
+      </c>
+      <c r="G25" s="50">
+        <v>3</v>
+      </c>
+      <c r="H25" s="51">
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A26" s="1"/>
-      <c r="B26" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="18">
-        <f>C25-G25</f>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="52">
+        <f>SUM(G21:G25)</f>
+        <v>19494</v>
+      </c>
+      <c r="H26" s="53">
+        <f>SUM(H21:H25)</f>
+        <v>19503</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A27" s="1"/>
+      <c r="B27" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="15">
+        <f>C10+C14+C16+C17+C22</f>
+        <v>87764</v>
+      </c>
+      <c r="D27" s="15">
+        <f>D10+D14+D16+D17+D22</f>
+        <v>87476</v>
+      </c>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A28" s="1"/>
+      <c r="B28" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="17">
+        <f>C27-G28</f>
         <v>0</v>
       </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-    </row>
-    <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="1"/>
-      <c r="B27" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="G28" s="54">
+        <f>G18+G26</f>
+        <v>87764</v>
+      </c>
+      <c r="H28" s="55">
+        <f>H18+H26</f>
+        <v>87476</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A29" s="1"/>
+      <c r="B29" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2609,7 +3607,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2622,26 +3620,26 @@
     <row r="1" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1"/>
-      <c r="B2" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="20" t="s">
+      <c r="B2" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="20" t="s">
-        <v>34</v>
+      <c r="D2" s="19" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1"/>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="20" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="1"/>
@@ -2650,65 +3648,66 @@
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1"/>
       <c r="B4" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="22">
+        <v>30</v>
+      </c>
+      <c r="C4" s="21">
         <v>64809</v>
       </c>
-      <c r="D4" s="23">
-        <f>IF(C$4=0,0,C4/C$4)</f>
+      <c r="D4" s="22">
+        <f t="shared" ref="D4:D19" si="0">IF(C$4=0,0,C4/C$4)</f>
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1"/>
       <c r="B5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="22">
+        <v>31</v>
+      </c>
+      <c r="C5" s="21">
         <v>43244</v>
       </c>
-      <c r="D5" s="23">
-        <f>IF(C$4=0,0,C5/C$4)</f>
+      <c r="D5" s="22">
+        <f t="shared" si="0"/>
         <v>0.66725300498387574</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1"/>
       <c r="B6" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="24">
-        <f>C4-C5</f>
-        <v>21565</v>
-      </c>
-      <c r="D6" s="23">
-        <f>IF(C$4=0,0,C6/C$4)</f>
-        <v>0.33274699501612431</v>
+        <v>32</v>
+      </c>
+      <c r="C6" s="23">
+        <v>5965</v>
+      </c>
+      <c r="D6" s="22">
+        <f t="shared" si="0"/>
+        <v>9.2039685846101615E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1"/>
       <c r="B7" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="22">
+        <v>33</v>
+      </c>
+      <c r="C7" s="21">
         <v>1413</v>
       </c>
-      <c r="D7" s="25">
-        <v>2.18025274267463E-2</v>
+      <c r="D7" s="24">
+        <f t="shared" si="0"/>
+        <v>2.1802527426746286E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1"/>
       <c r="B8" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="26">
+        <v>34</v>
+      </c>
+      <c r="C8" s="25">
+        <f>C4-C5-C6-C7</f>
         <v>14187</v>
       </c>
-      <c r="D8" s="23">
-        <f>IF(C$4=0,0,C8/C$4)</f>
+      <c r="D8" s="22">
+        <f t="shared" si="0"/>
         <v>0.21890478174327641</v>
       </c>
     </row>
@@ -2716,133 +3715,135 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="27">
-        <f>IF(C$4=0,0,C9/C$4)</f>
+      <c r="D9" s="26">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="22">
+        <v>35</v>
+      </c>
+      <c r="C10" s="21">
         <v>2116</v>
       </c>
-      <c r="D10" s="23">
-        <f>IF(C$4=0,0,C10/C$4)</f>
+      <c r="D10" s="22">
+        <f t="shared" si="0"/>
         <v>3.264978629511333E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="22">
+        <v>36</v>
+      </c>
+      <c r="C11" s="21">
         <v>1713</v>
       </c>
-      <c r="D11" s="25">
-        <v>2.64315141415544E-2</v>
+      <c r="D11" s="24">
+        <f t="shared" si="0"/>
+        <v>2.6431514141554414E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1"/>
       <c r="B12" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="24">
-        <f>C6-C8-C9-C10</f>
-        <v>5262</v>
-      </c>
-      <c r="D12" s="23">
-        <f>IF(C$4=0,0,C12/C$4)</f>
-        <v>8.1192426977734572E-2</v>
+        <v>37</v>
+      </c>
+      <c r="C12" s="23">
+        <f>C8+C10-C11</f>
+        <v>14590</v>
+      </c>
+      <c r="D12" s="22">
+        <f t="shared" si="0"/>
+        <v>0.22512305389683532</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="27">
-        <f>IF(C$4=0,0,C13/C$4)</f>
+      <c r="D13" s="26">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1"/>
       <c r="B14" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="22">
+        <v>38</v>
+      </c>
+      <c r="C14" s="21">
         <v>2944</v>
       </c>
-      <c r="D14" s="25">
-        <v>4.5425789627983798E-2</v>
+      <c r="D14" s="24">
+        <f t="shared" si="0"/>
+        <v>4.542578962798377E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="1"/>
       <c r="B15" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="24">
-        <f>C12-C13</f>
-        <v>5262</v>
-      </c>
-      <c r="D15" s="23">
-        <f>IF(C$4=0,0,C15/C$4)</f>
-        <v>8.1192426977734572E-2</v>
+        <v>39</v>
+      </c>
+      <c r="C15" s="23">
+        <f>C12-C14</f>
+        <v>11646</v>
+      </c>
+      <c r="D15" s="22">
+        <f t="shared" si="0"/>
+        <v>0.17969726426885155</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
-      <c r="D16" s="27">
-        <f>IF(C$4=0,0,C16/C$4)</f>
+      <c r="D16" s="26">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1"/>
       <c r="B17" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="28">
+        <v>40</v>
+      </c>
+      <c r="C17" s="27">
         <f>C15-C16</f>
-        <v>5262</v>
-      </c>
-      <c r="D17" s="27">
-        <f>IF(C$4=0,0,C17/C$4)</f>
-        <v>8.1192426977734572E-2</v>
+        <v>11646</v>
+      </c>
+      <c r="D17" s="26">
+        <f t="shared" si="0"/>
+        <v>0.17969726426885155</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="22">
+        <v>41</v>
+      </c>
+      <c r="C18" s="21">
         <v>2736</v>
       </c>
-      <c r="D18" s="23">
-        <f>IF(C$4=0,0,C18/C$4)</f>
+      <c r="D18" s="22">
+        <f t="shared" si="0"/>
         <v>4.221635883905013E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="24">
+        <v>42</v>
+      </c>
+      <c r="C19" s="23">
         <f>C17-C18</f>
-        <v>2526</v>
-      </c>
-      <c r="D19" s="23">
-        <f>IF(C$4=0,0,C19/C$4)</f>
-        <v>3.8976068138684442E-2</v>
+        <v>8910</v>
+      </c>
+      <c r="D19" s="22">
+        <f t="shared" si="0"/>
+        <v>0.1374809054298014</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.45">
@@ -2853,8 +3854,8 @@
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="1"/>
-      <c r="B21" s="21" t="s">
-        <v>31</v>
+      <c r="B21" s="20" t="s">
+        <v>26</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -2862,6 +3863,7 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2879,26 +3881,26 @@
     <row r="1" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1"/>
-      <c r="B2" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="20" t="s">
+      <c r="B2" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="20" t="s">
-        <v>49</v>
+      <c r="D2" s="19" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1"/>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="20" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="1"/>
@@ -2907,7 +3909,7 @@
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1"/>
       <c r="B4" s="7" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -2915,116 +3917,121 @@
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1"/>
       <c r="B5" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="22">
+        <v>39</v>
+      </c>
+      <c r="C5" s="21">
         <v>11646</v>
       </c>
-      <c r="D5" s="29" t="s">
-        <v>51</v>
+      <c r="D5" s="28" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1"/>
       <c r="B6" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="22">
+        <v>47</v>
+      </c>
+      <c r="C6" s="21">
         <v>1413</v>
       </c>
-      <c r="D6" s="29" t="s">
-        <v>51</v>
+      <c r="D6" s="28" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1"/>
       <c r="B7" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="29"/>
+        <v>48</v>
+      </c>
+      <c r="C7" s="21"/>
+      <c r="D7" s="28"/>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1"/>
       <c r="B8" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" s="22">
-        <v>-128</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="C8" s="21">
+        <f>-('Balance Sheet'!C6-'Balance Sheet'!D6)</f>
+        <v>28</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="22">
-        <v>1217</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>55</v>
+        <v>51</v>
+      </c>
+      <c r="C9" s="21">
+        <f>-('Balance Sheet'!C8-'Balance Sheet'!D8)</f>
+        <v>-262</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="22">
-        <v>-135</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="C10" s="21">
+        <f>-('Balance Sheet'!C9-'Balance Sheet'!D9)</f>
+        <v>1467</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="22">
-        <v>-144</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>55</v>
+        <v>53</v>
+      </c>
+      <c r="C11" s="21">
+        <f>'Balance Sheet'!G6-'Balance Sheet'!H6</f>
+        <v>-231</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="22">
-        <v>-149</v>
-      </c>
-      <c r="D12" s="29" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="C12" s="21">
+        <f>SUM('Balance Sheet'!G7:G11)-SUM('Balance Sheet'!H7:H11)</f>
+        <v>123</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="1"/>
       <c r="B13" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="24">
+        <v>55</v>
+      </c>
+      <c r="C13" s="23">
         <f>SUM(C8:C12)</f>
-        <v>661</v>
-      </c>
-      <c r="D13" s="29"/>
+        <v>1125</v>
+      </c>
+      <c r="D13" s="28"/>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1"/>
       <c r="B14" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="24">
+        <v>56</v>
+      </c>
+      <c r="C14" s="23">
         <f>C5+C6+C13</f>
-        <v>13720</v>
-      </c>
-      <c r="D14" s="29"/>
+        <v>14184</v>
+      </c>
+      <c r="D14" s="28"/>
     </row>
     <row r="15" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="1"/>
@@ -3035,7 +4042,7 @@
     <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="1"/>
       <c r="B16" s="7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
@@ -3043,43 +4050,43 @@
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" s="22">
+        <v>58</v>
+      </c>
+      <c r="C17" s="21">
         <v>-1702</v>
       </c>
-      <c r="D17" s="29"/>
+      <c r="D17" s="28"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="22">
+        <v>59</v>
+      </c>
+      <c r="C18" s="21">
         <v>298</v>
       </c>
-      <c r="D18" s="29"/>
+      <c r="D18" s="28"/>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="22">
+        <v>60</v>
+      </c>
+      <c r="C19" s="21">
         <v>-782</v>
       </c>
-      <c r="D19" s="29"/>
+      <c r="D19" s="28"/>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1"/>
       <c r="B20" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="24">
+        <v>61</v>
+      </c>
+      <c r="C20" s="23">
         <f>SUM(C17:C19)</f>
         <v>-2186</v>
       </c>
-      <c r="D20" s="29"/>
+      <c r="D20" s="28"/>
     </row>
     <row r="21" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="1"/>
@@ -3090,7 +4097,7 @@
     <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1"/>
       <c r="B22" s="7" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -3098,63 +4105,63 @@
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="1"/>
       <c r="B23" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" s="22">
+        <v>63</v>
+      </c>
+      <c r="C23" s="21">
         <v>689</v>
       </c>
-      <c r="D23" s="29"/>
+      <c r="D23" s="28"/>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="1"/>
       <c r="B24" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="22">
+        <v>64</v>
+      </c>
+      <c r="C24" s="21">
         <v>-61</v>
       </c>
-      <c r="D24" s="29"/>
+      <c r="D24" s="28"/>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1"/>
       <c r="B25" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="22">
+        <v>65</v>
+      </c>
+      <c r="C25" s="21">
         <v>-2736</v>
       </c>
-      <c r="D25" s="29"/>
+      <c r="D25" s="28"/>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="1"/>
       <c r="B26" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" s="22">
+        <v>66</v>
+      </c>
+      <c r="C26" s="21">
         <v>-7839</v>
       </c>
-      <c r="D26" s="29"/>
+      <c r="D26" s="28"/>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="1"/>
       <c r="B27" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="22">
+        <v>67</v>
+      </c>
+      <c r="C27" s="21">
         <v>-327</v>
       </c>
-      <c r="D27" s="29"/>
+      <c r="D27" s="28"/>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="1"/>
       <c r="B28" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C28" s="24">
+        <v>68</v>
+      </c>
+      <c r="C28" s="23">
         <f>SUM(C23:C27)</f>
         <v>-10274</v>
       </c>
-      <c r="D28" s="29"/>
+      <c r="D28" s="28"/>
     </row>
     <row r="29" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="1"/>
@@ -3165,13 +4172,13 @@
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="1"/>
       <c r="B30" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C30" s="24">
+        <v>69</v>
+      </c>
+      <c r="C30" s="23">
         <f>C14+C20+C28</f>
-        <v>1260</v>
-      </c>
-      <c r="D30" s="29"/>
+        <v>1724</v>
+      </c>
+      <c r="D30" s="28"/>
     </row>
     <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A31" s="1"/>
@@ -3181,8 +4188,8 @@
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="1"/>
-      <c r="B32" s="21" t="s">
-        <v>31</v>
+      <c r="B32" s="20" t="s">
+        <v>26</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -3208,7 +4215,7 @@
     <row r="1" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3216,113 +4223,113 @@
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1"/>
-      <c r="B2" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>79</v>
+      <c r="B2" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1"/>
       <c r="B3" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="30">
+        <v>75</v>
+      </c>
+      <c r="C3" s="29">
         <v>2024</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="32" t="s">
-        <v>81</v>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1"/>
       <c r="B4" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="30">
+        <v>77</v>
+      </c>
+      <c r="C4" s="29">
         <v>2023</v>
       </c>
-      <c r="D4" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>84</v>
+      <c r="D4" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1"/>
       <c r="B5" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" s="30">
+        <v>80</v>
+      </c>
+      <c r="C5" s="29">
         <v>349.58</v>
       </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="32" t="s">
-        <v>86</v>
+      <c r="D5" s="30"/>
+      <c r="E5" s="31" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1"/>
       <c r="B6" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="30">
+        <v>82</v>
+      </c>
+      <c r="C6" s="29">
         <v>492</v>
       </c>
-      <c r="D6" s="31"/>
-      <c r="E6" s="32" t="s">
-        <v>88</v>
+      <c r="D6" s="30"/>
+      <c r="E6" s="31" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1"/>
       <c r="B7" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="C7" s="30">
+        <v>84</v>
+      </c>
+      <c r="C7" s="29">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="32" t="s">
-        <v>90</v>
+      <c r="D7" s="30"/>
+      <c r="E7" s="31" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1"/>
       <c r="B8" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" s="30">
+        <v>86</v>
+      </c>
+      <c r="C8" s="29">
         <v>0.214</v>
       </c>
-      <c r="D8" s="31"/>
-      <c r="E8" s="32" t="s">
-        <v>92</v>
+      <c r="D8" s="30"/>
+      <c r="E8" s="31" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" s="33">
+        <v>88</v>
+      </c>
+      <c r="C9" s="32">
         <f>C5*C6</f>
         <v>171993.36</v>
       </c>
-      <c r="D9" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" s="32" t="s">
-        <v>95</v>
+      <c r="D9" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.45">
@@ -3335,7 +4342,7 @@
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1"/>
       <c r="B11" s="7" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -3344,81 +4351,81 @@
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="24">
-        <f>'Balance Sheet'!H23</f>
-        <v>28962</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" s="32" t="s">
-        <v>99</v>
+        <v>92</v>
+      </c>
+      <c r="C12" s="23">
+        <f>'Balance Sheet'!H22</f>
+        <v>-36339</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" s="31" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="24">
+        <v>95</v>
+      </c>
+      <c r="C13" s="23">
         <f>'Balance Sheet'!D8</f>
         <v>16565</v>
       </c>
-      <c r="D13" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="E13" s="32" t="s">
-        <v>102</v>
+      <c r="D13" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1"/>
       <c r="B14" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="24">
+        <v>98</v>
+      </c>
+      <c r="C14" s="23">
         <f>'Balance Sheet'!D6</f>
         <v>9310</v>
       </c>
-      <c r="D14" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="E14" s="32" t="s">
-        <v>105</v>
+      <c r="D14" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" s="31" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="1"/>
       <c r="B15" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C15" s="24">
-        <f>'Balance Sheet'!D25</f>
-        <v>82432</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="E15" s="32" t="s">
-        <v>108</v>
+        <v>101</v>
+      </c>
+      <c r="C15" s="23">
+        <f>'Balance Sheet'!D27</f>
+        <v>87476</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C16" s="24">
-        <f>'Balance Sheet'!H11+'Balance Sheet'!H23</f>
-        <v>54069</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="E16" s="32" t="s">
-        <v>111</v>
+        <v>104</v>
+      </c>
+      <c r="C16" s="23">
+        <f>'Balance Sheet'!H11+'Balance Sheet'!H22</f>
+        <v>-33216</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" s="31" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.45">
@@ -3431,7 +4438,7 @@
     <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="1"/>
       <c r="B18" s="7" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
@@ -3440,193 +4447,193 @@
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C19" s="34">
+        <v>108</v>
+      </c>
+      <c r="C19" s="33">
         <f>'Income Statement'!C17+(1-C8)*'Income Statement'!C13</f>
-        <v>5262</v>
-      </c>
-      <c r="D19" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="E19" s="32" t="s">
-        <v>115</v>
+        <v>11646</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="E19" s="31" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C20" s="33">
+        <v>111</v>
+      </c>
+      <c r="C20" s="32">
         <f>'Income Statement'!C4/365</f>
         <v>177.55890410958904</v>
       </c>
-      <c r="D20" s="31" t="s">
-        <v>117</v>
-      </c>
-      <c r="E20" s="32" t="s">
-        <v>118</v>
+      <c r="D20" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" s="31" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="1"/>
       <c r="B21" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C21" s="24">
-        <f>'Balance Sheet'!G23</f>
-        <v>32181</v>
-      </c>
-      <c r="D21" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="E21" s="32" t="s">
-        <v>121</v>
+        <v>114</v>
+      </c>
+      <c r="C21" s="23">
+        <f>'Balance Sheet'!G22</f>
+        <v>-44331</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="E21" s="31" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1"/>
       <c r="B22" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C22" s="24">
+        <v>117</v>
+      </c>
+      <c r="C22" s="23">
         <f>'Balance Sheet'!C5</f>
         <v>6889</v>
       </c>
-      <c r="D22" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="E22" s="32" t="s">
-        <v>124</v>
+      <c r="D22" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="E22" s="31" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="1"/>
       <c r="B23" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C23" s="24">
+        <v>120</v>
+      </c>
+      <c r="C23" s="23">
         <f>'Balance Sheet'!C10</f>
         <v>45682</v>
       </c>
-      <c r="D23" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="E23" s="32" t="s">
-        <v>127</v>
+      <c r="D23" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="E23" s="31" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="1"/>
       <c r="B24" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C24" s="24">
+        <v>123</v>
+      </c>
+      <c r="C24" s="23">
         <f>'Balance Sheet'!G9</f>
-        <v>20075</v>
-      </c>
-      <c r="D24" s="31" t="s">
-        <v>129</v>
-      </c>
-      <c r="E24" s="32" t="s">
-        <v>130</v>
+        <v>2322</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="E24" s="31" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1"/>
       <c r="B25" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="C25" s="33">
+        <v>126</v>
+      </c>
+      <c r="C25" s="32">
         <f>'Income Statement'!C5/365</f>
         <v>118.47671232876712</v>
       </c>
-      <c r="D25" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="E25" s="32" t="s">
-        <v>133</v>
+      <c r="D25" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="E25" s="31" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="1"/>
       <c r="B26" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C26" s="24">
+        <v>129</v>
+      </c>
+      <c r="C26" s="23">
         <f>'Balance Sheet'!G11</f>
-        <v>25046</v>
-      </c>
-      <c r="D26" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="E26" s="32" t="s">
-        <v>136</v>
+        <v>2909</v>
+      </c>
+      <c r="D26" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26" s="31" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="1"/>
       <c r="B27" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="C27" s="24">
+        <v>132</v>
+      </c>
+      <c r="C27" s="23">
         <f>'Balance Sheet'!C10-'Balance Sheet'!G9</f>
-        <v>25607</v>
-      </c>
-      <c r="D27" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="E27" s="32" t="s">
-        <v>139</v>
+        <v>43360</v>
+      </c>
+      <c r="D27" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="E27" s="31" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="1"/>
       <c r="B28" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="C28" s="24">
-        <f>'Balance Sheet'!C25</f>
-        <v>86028</v>
-      </c>
-      <c r="D28" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="E28" s="32" t="s">
-        <v>142</v>
+        <v>135</v>
+      </c>
+      <c r="C28" s="23">
+        <f>'Balance Sheet'!C27</f>
+        <v>87764</v>
+      </c>
+      <c r="D28" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="E28" s="31" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="1"/>
       <c r="B29" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="C29" s="24">
-        <f>'Balance Sheet'!G11+'Balance Sheet'!G23</f>
-        <v>57227</v>
-      </c>
-      <c r="D29" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="E29" s="32" t="s">
-        <v>145</v>
+        <v>138</v>
+      </c>
+      <c r="C29" s="23">
+        <f>'Balance Sheet'!G11+'Balance Sheet'!G22</f>
+        <v>-41422</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="E29" s="31" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="1"/>
       <c r="B30" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="C30" s="24">
+        <v>141</v>
+      </c>
+      <c r="C30" s="23">
         <f>'Balance Sheet'!G14</f>
-        <v>53847</v>
-      </c>
-      <c r="D30" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="E30" s="32" t="s">
-        <v>148</v>
+        <v>0</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="E30" s="31" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.45">
@@ -3639,7 +4646,7 @@
     <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="1"/>
       <c r="B32" s="7" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -3648,65 +4655,65 @@
     <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="1"/>
       <c r="B33" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="C33" s="24">
+        <v>145</v>
+      </c>
+      <c r="C33" s="23">
         <f>AVERAGE(C12,C21)</f>
-        <v>30571.5</v>
-      </c>
-      <c r="D33" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="E33" s="32" t="s">
-        <v>152</v>
+        <v>-40335</v>
+      </c>
+      <c r="D33" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="E33" s="31" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="1"/>
       <c r="B34" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C34" s="24">
+        <v>148</v>
+      </c>
+      <c r="C34" s="23">
         <f>AVERAGE(C15,C28)</f>
-        <v>84230</v>
-      </c>
-      <c r="D34" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="E34" s="32" t="s">
-        <v>155</v>
+        <v>87620</v>
+      </c>
+      <c r="D34" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="E34" s="31" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="1"/>
       <c r="B35" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="C35" s="24">
+        <v>151</v>
+      </c>
+      <c r="C35" s="23">
         <f>AVERAGE(C16,C29)</f>
-        <v>55648</v>
-      </c>
-      <c r="D35" s="31" t="s">
-        <v>157</v>
-      </c>
-      <c r="E35" s="32" t="s">
-        <v>158</v>
+        <v>-37319</v>
+      </c>
+      <c r="D35" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="E35" s="31" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="1"/>
       <c r="B36" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="C36" s="24">
+        <v>154</v>
+      </c>
+      <c r="C36" s="23">
         <f>C26+C21</f>
-        <v>57227</v>
-      </c>
-      <c r="D36" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="E36" s="32" t="s">
-        <v>161</v>
+        <v>-41422</v>
+      </c>
+      <c r="D36" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="E36" s="31" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.45">
@@ -3725,23 +4732,23 @@
     </row>
     <row r="39" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="1"/>
-      <c r="B39" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="E39" s="20" t="s">
-        <v>79</v>
+      <c r="B39" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="D39" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="1"/>
       <c r="B40" s="7" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
@@ -3750,35 +4757,35 @@
     <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="1"/>
       <c r="B41" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="C41" s="35"/>
-      <c r="D41" s="31" t="s">
-        <v>167</v>
-      </c>
-      <c r="E41" s="32"/>
+        <v>161</v>
+      </c>
+      <c r="C41" s="34"/>
+      <c r="D41" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="E41" s="31"/>
     </row>
     <row r="42" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="1"/>
       <c r="B42" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="C42" s="35"/>
-      <c r="D42" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="E42" s="32"/>
+        <v>163</v>
+      </c>
+      <c r="C42" s="34"/>
+      <c r="D42" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="E42" s="31"/>
     </row>
     <row r="43" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="1"/>
       <c r="B43" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="C43" s="35"/>
-      <c r="D43" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="E43" s="32"/>
+        <v>165</v>
+      </c>
+      <c r="C43" s="34"/>
+      <c r="D43" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="E43" s="31"/>
     </row>
     <row r="44" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="1"/>
@@ -3790,7 +4797,7 @@
     <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="1"/>
       <c r="B45" s="7" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
@@ -3799,68 +4806,68 @@
     <row r="46" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="1"/>
       <c r="B46" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="C46" s="35"/>
-      <c r="D46" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="E46" s="32"/>
+        <v>168</v>
+      </c>
+      <c r="C46" s="34"/>
+      <c r="D46" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="E46" s="31"/>
     </row>
     <row r="47" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="1"/>
       <c r="B47" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="C47" s="35"/>
-      <c r="D47" s="31" t="s">
-        <v>176</v>
-      </c>
-      <c r="E47" s="32"/>
+        <v>170</v>
+      </c>
+      <c r="C47" s="34"/>
+      <c r="D47" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="E47" s="31"/>
     </row>
     <row r="48" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="1"/>
       <c r="B48" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="C48" s="35"/>
-      <c r="D48" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="E48" s="32"/>
+        <v>172</v>
+      </c>
+      <c r="C48" s="34"/>
+      <c r="D48" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="E48" s="31"/>
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="1"/>
       <c r="B49" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="C49" s="35"/>
-      <c r="D49" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="E49" s="32"/>
+        <v>174</v>
+      </c>
+      <c r="C49" s="34"/>
+      <c r="D49" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="E49" s="31"/>
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="1"/>
       <c r="B50" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="C50" s="35"/>
-      <c r="D50" s="31" t="s">
-        <v>182</v>
-      </c>
-      <c r="E50" s="32"/>
+        <v>176</v>
+      </c>
+      <c r="C50" s="34"/>
+      <c r="D50" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="E50" s="31"/>
     </row>
     <row r="51" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="1"/>
       <c r="B51" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="C51" s="35"/>
-      <c r="D51" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="E51" s="32"/>
+        <v>178</v>
+      </c>
+      <c r="C51" s="34"/>
+      <c r="D51" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="E51" s="31"/>
     </row>
     <row r="52" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="1"/>
@@ -3872,7 +4879,7 @@
     <row r="53" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="1"/>
       <c r="B53" s="7" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
@@ -3881,82 +4888,82 @@
     <row r="54" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="1"/>
       <c r="B54" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="C54" s="35"/>
-      <c r="D54" s="31" t="s">
-        <v>187</v>
-      </c>
-      <c r="E54" s="32" t="s">
-        <v>188</v>
+        <v>181</v>
+      </c>
+      <c r="C54" s="34"/>
+      <c r="D54" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="E54" s="31" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="1"/>
       <c r="B55" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="C55" s="35"/>
-      <c r="D55" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="E55" s="32"/>
+        <v>184</v>
+      </c>
+      <c r="C55" s="34"/>
+      <c r="D55" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="E55" s="31"/>
     </row>
     <row r="56" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="1"/>
       <c r="B56" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="C56" s="35"/>
-      <c r="D56" s="31" t="s">
-        <v>192</v>
-      </c>
-      <c r="E56" s="32"/>
+        <v>186</v>
+      </c>
+      <c r="C56" s="34"/>
+      <c r="D56" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="E56" s="31"/>
     </row>
     <row r="57" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="1"/>
       <c r="B57" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="C57" s="35"/>
-      <c r="D57" s="31" t="s">
-        <v>194</v>
-      </c>
-      <c r="E57" s="32"/>
+        <v>188</v>
+      </c>
+      <c r="C57" s="34"/>
+      <c r="D57" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="E57" s="31"/>
     </row>
     <row r="58" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="1"/>
       <c r="B58" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="C58" s="35"/>
-      <c r="D58" s="31" t="s">
-        <v>196</v>
-      </c>
-      <c r="E58" s="32"/>
+        <v>190</v>
+      </c>
+      <c r="C58" s="34"/>
+      <c r="D58" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="E58" s="31"/>
     </row>
     <row r="59" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="1"/>
       <c r="B59" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="C59" s="35"/>
-      <c r="D59" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="E59" s="32"/>
+        <v>192</v>
+      </c>
+      <c r="C59" s="34"/>
+      <c r="D59" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="E59" s="31"/>
     </row>
     <row r="60" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="1"/>
       <c r="B60" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="C60" s="35"/>
-      <c r="D60" s="31" t="s">
-        <v>200</v>
-      </c>
-      <c r="E60" s="32" t="s">
-        <v>201</v>
+        <v>194</v>
+      </c>
+      <c r="C60" s="34"/>
+      <c r="D60" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="E60" s="31" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.45">
@@ -3969,7 +4976,7 @@
     <row r="62" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="1"/>
       <c r="B62" s="7" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C62" s="8"/>
       <c r="D62" s="8"/>
@@ -3978,82 +4985,82 @@
     <row r="63" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="1"/>
       <c r="B63" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="C63" s="35"/>
-      <c r="D63" s="31" t="s">
-        <v>204</v>
-      </c>
-      <c r="E63" s="32"/>
+        <v>198</v>
+      </c>
+      <c r="C63" s="34"/>
+      <c r="D63" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="E63" s="31"/>
     </row>
     <row r="64" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="1"/>
       <c r="B64" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="C64" s="35"/>
-      <c r="D64" s="31" t="s">
-        <v>206</v>
-      </c>
-      <c r="E64" s="32"/>
+        <v>200</v>
+      </c>
+      <c r="C64" s="34"/>
+      <c r="D64" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="E64" s="31"/>
     </row>
     <row r="65" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="1"/>
       <c r="B65" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="C65" s="35"/>
-      <c r="D65" s="31" t="s">
-        <v>208</v>
-      </c>
-      <c r="E65" s="32"/>
+        <v>202</v>
+      </c>
+      <c r="C65" s="34"/>
+      <c r="D65" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="E65" s="31"/>
     </row>
     <row r="66" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="1"/>
       <c r="B66" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="C66" s="35"/>
-      <c r="D66" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="E66" s="32"/>
+        <v>204</v>
+      </c>
+      <c r="C66" s="34"/>
+      <c r="D66" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="E66" s="31"/>
     </row>
     <row r="67" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="1"/>
       <c r="B67" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="C67" s="35"/>
-      <c r="D67" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="E67" s="32"/>
+        <v>206</v>
+      </c>
+      <c r="C67" s="34"/>
+      <c r="D67" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E67" s="31"/>
     </row>
     <row r="68" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="1"/>
       <c r="B68" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="C68" s="35"/>
-      <c r="D68" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="E68" s="32" t="s">
-        <v>215</v>
+        <v>208</v>
+      </c>
+      <c r="C68" s="34"/>
+      <c r="D68" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E68" s="31" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="1"/>
       <c r="B69" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="C69" s="35"/>
-      <c r="D69" s="31" t="s">
-        <v>217</v>
-      </c>
-      <c r="E69" s="32" t="s">
-        <v>218</v>
+        <v>211</v>
+      </c>
+      <c r="C69" s="34"/>
+      <c r="D69" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="E69" s="31" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.45">
@@ -4066,7 +5073,7 @@
     <row r="71" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="1"/>
       <c r="B71" s="7" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
@@ -4075,46 +5082,46 @@
     <row r="72" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="1"/>
       <c r="B72" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="C72" s="35"/>
-      <c r="D72" s="31" t="s">
-        <v>221</v>
-      </c>
-      <c r="E72" s="32"/>
+        <v>215</v>
+      </c>
+      <c r="C72" s="34"/>
+      <c r="D72" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E72" s="31"/>
     </row>
     <row r="73" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="1"/>
       <c r="B73" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="C73" s="35"/>
-      <c r="D73" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="E73" s="32"/>
+        <v>217</v>
+      </c>
+      <c r="C73" s="34"/>
+      <c r="D73" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E73" s="31"/>
     </row>
     <row r="74" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="1"/>
       <c r="B74" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="C74" s="35"/>
-      <c r="D74" s="31" t="s">
-        <v>225</v>
-      </c>
-      <c r="E74" s="32"/>
+        <v>219</v>
+      </c>
+      <c r="C74" s="34"/>
+      <c r="D74" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="E74" s="31"/>
     </row>
     <row r="75" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="1"/>
       <c r="B75" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="C75" s="35"/>
-      <c r="D75" s="31" t="s">
-        <v>227</v>
-      </c>
-      <c r="E75" s="32"/>
+        <v>221</v>
+      </c>
+      <c r="C75" s="34"/>
+      <c r="D75" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="E75" s="31"/>
     </row>
     <row r="76" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="1"/>
@@ -4126,7 +5133,7 @@
     <row r="77" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="1"/>
       <c r="B77" s="7" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="8"/>
@@ -4135,38 +5142,38 @@
     <row r="78" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="1"/>
       <c r="B78" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="C78" s="35"/>
-      <c r="D78" s="31" t="s">
-        <v>230</v>
-      </c>
-      <c r="E78" s="32"/>
+        <v>224</v>
+      </c>
+      <c r="C78" s="34"/>
+      <c r="D78" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="E78" s="31"/>
     </row>
     <row r="79" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="1"/>
-      <c r="B79" s="36" t="s">
-        <v>231</v>
-      </c>
-      <c r="C79" s="35"/>
-      <c r="D79" s="31" t="s">
-        <v>232</v>
-      </c>
-      <c r="E79" s="32" t="s">
-        <v>188</v>
+      <c r="B79" s="35" t="s">
+        <v>226</v>
+      </c>
+      <c r="C79" s="34"/>
+      <c r="D79" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="E79" s="31" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="1"/>
-      <c r="B80" s="36" t="s">
-        <v>233</v>
-      </c>
-      <c r="C80" s="35"/>
-      <c r="D80" s="31" t="s">
-        <v>232</v>
-      </c>
-      <c r="E80" s="32" t="s">
-        <v>201</v>
+      <c r="B80" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="C80" s="34"/>
+      <c r="D80" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="E80" s="31" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.45">
@@ -4179,64 +5186,64 @@
     <row r="82" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="1"/>
       <c r="B82" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="C82" s="35"/>
-      <c r="D82" s="31" t="s">
-        <v>235</v>
-      </c>
-      <c r="E82" s="32"/>
+        <v>229</v>
+      </c>
+      <c r="C82" s="34"/>
+      <c r="D82" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="E82" s="31"/>
     </row>
     <row r="83" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="1"/>
-      <c r="B83" s="36" t="s">
-        <v>236</v>
-      </c>
-      <c r="C83" s="35"/>
-      <c r="D83" s="31" t="s">
-        <v>237</v>
-      </c>
-      <c r="E83" s="32" t="s">
-        <v>218</v>
+      <c r="B83" s="35" t="s">
+        <v>231</v>
+      </c>
+      <c r="C83" s="34"/>
+      <c r="D83" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="E83" s="31" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="1"/>
-      <c r="B84" s="36" t="s">
-        <v>231</v>
-      </c>
-      <c r="C84" s="35"/>
-      <c r="D84" s="31" t="s">
-        <v>232</v>
-      </c>
-      <c r="E84" s="32" t="s">
-        <v>188</v>
+      <c r="B84" s="35" t="s">
+        <v>226</v>
+      </c>
+      <c r="C84" s="34"/>
+      <c r="D84" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="E84" s="31" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="1"/>
-      <c r="B85" s="36" t="s">
-        <v>233</v>
-      </c>
-      <c r="C85" s="35"/>
-      <c r="D85" s="31" t="s">
-        <v>232</v>
-      </c>
-      <c r="E85" s="32" t="s">
-        <v>201</v>
+      <c r="B85" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="C85" s="34"/>
+      <c r="D85" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="E85" s="31" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="1"/>
-      <c r="B86" s="36" t="s">
-        <v>238</v>
-      </c>
-      <c r="C86" s="35"/>
-      <c r="D86" s="31" t="s">
-        <v>237</v>
-      </c>
-      <c r="E86" s="32" t="s">
-        <v>215</v>
+      <c r="B86" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="C86" s="34"/>
+      <c r="D86" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="E86" s="31" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.45">
@@ -4255,23 +5262,23 @@
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="1"/>
-      <c r="B89" s="37" t="s">
-        <v>239</v>
-      </c>
-      <c r="C89" s="38" t="s">
-        <v>240</v>
-      </c>
-      <c r="D89" s="39" t="s">
-        <v>241</v>
-      </c>
-      <c r="E89" s="40" t="s">
-        <v>242</v>
+      <c r="B89" s="36" t="s">
+        <v>234</v>
+      </c>
+      <c r="C89" s="37" t="s">
+        <v>235</v>
+      </c>
+      <c r="D89" s="38" t="s">
+        <v>236</v>
+      </c>
+      <c r="E89" s="39" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="1"/>
-      <c r="B90" s="21" t="s">
-        <v>31</v>
+      <c r="B90" s="20" t="s">
+        <v>26</v>
       </c>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
@@ -4301,8 +5308,8 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1"/>
-      <c r="B1" s="41" t="s">
-        <v>243</v>
+      <c r="B1" s="40" t="s">
+        <v>238</v>
       </c>
       <c r="C1" s="1"/>
     </row>
@@ -4313,156 +5320,156 @@
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1"/>
-      <c r="B3" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="C3" s="43" t="s">
-        <v>245</v>
+      <c r="B3" s="41" t="s">
+        <v>239</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1"/>
-      <c r="B4" s="42" t="s">
-        <v>246</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>247</v>
+      <c r="B4" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1"/>
-      <c r="B5" s="42" t="s">
-        <v>248</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>249</v>
+      <c r="B5" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1"/>
-      <c r="B6" s="42" t="s">
-        <v>250</v>
-      </c>
-      <c r="C6" s="43" t="s">
+      <c r="B6" s="41" t="s">
+        <v>245</v>
+      </c>
+      <c r="C6" s="42" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1"/>
-      <c r="B7" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="C7" s="43" t="s">
+      <c r="B7" s="41" t="s">
+        <v>246</v>
+      </c>
+      <c r="C7" s="42" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1"/>
-      <c r="B8" s="42" t="s">
-        <v>252</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>253</v>
+      <c r="B8" s="41" t="s">
+        <v>247</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="1"/>
-      <c r="B9" s="42" t="s">
-        <v>254</v>
-      </c>
-      <c r="C9" s="43" t="s">
-        <v>255</v>
+      <c r="B9" s="41" t="s">
+        <v>249</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1"/>
-      <c r="B10" s="42" t="s">
-        <v>256</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>257</v>
+      <c r="B10" s="41" t="s">
+        <v>251</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1"/>
-      <c r="B11" s="42" t="s">
-        <v>258</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>259</v>
+      <c r="B11" s="41" t="s">
+        <v>253</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1"/>
-      <c r="B12" s="42" t="s">
-        <v>260</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>261</v>
+      <c r="B12" s="41" t="s">
+        <v>255</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="1"/>
-      <c r="B13" s="42" t="s">
-        <v>262</v>
-      </c>
-      <c r="C13" s="43" t="s">
-        <v>263</v>
+      <c r="B13" s="41" t="s">
+        <v>257</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
-      <c r="C14" s="43"/>
+      <c r="C14" s="42"/>
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="1"/>
-      <c r="B15" s="42" t="s">
-        <v>264</v>
-      </c>
-      <c r="C15" s="43" t="s">
-        <v>265</v>
+      <c r="B15" s="41" t="s">
+        <v>259</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="1"/>
-      <c r="B16" s="42" t="s">
-        <v>266</v>
-      </c>
-      <c r="C16" s="43" t="s">
-        <v>267</v>
+      <c r="B16" s="41" t="s">
+        <v>261</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1"/>
-      <c r="B17" s="42" t="s">
-        <v>268</v>
-      </c>
-      <c r="C17" s="43" t="s">
-        <v>269</v>
+      <c r="B17" s="41" t="s">
+        <v>263</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="1"/>
-      <c r="B18" s="42" t="s">
-        <v>270</v>
-      </c>
-      <c r="C18" s="43" t="s">
-        <v>271</v>
+      <c r="B18" s="41" t="s">
+        <v>265</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
-      <c r="C19" s="43"/>
+      <c r="C19" s="42"/>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1"/>
-      <c r="B20" s="42" t="s">
-        <v>272</v>
-      </c>
-      <c r="C20" s="43" t="s">
-        <v>273</v>
+      <c r="B20" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="C20" s="42" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>

--- a/courses/BUS-314-International-Corporate-Finance/accounting-ratios/_scenarios/BUS314_CAT_Scenario.xlsx
+++ b/courses/BUS-314-International-Corporate-Finance/accounting-ratios/_scenarios/BUS314_CAT_Scenario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\shidler\courses\BUS-314-International-Corporate-Finance\accounting-ratios\_scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031443C3-FA8E-42D4-A778-75C91182DCB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480CD546-C7D5-49BA-AEFD-A67979C0466B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
